--- a/test/fixtures/xlsx/composite-key/composite-key.xlsx
+++ b/test/fixtures/xlsx/composite-key/composite-key.xlsx
@@ -10,12 +10,13 @@
     <sheet name="Loadout" sheetId="2" r:id="rId4"/>
     <sheet name="Route" sheetId="3" r:id="rId5"/>
     <sheet name="Grid" sheetId="4" r:id="rId6"/>
+    <sheet name="Link" sheetId="5" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="97">
   <si>
     <t xml:space="preserve">:enum Slot</t>
   </si>
@@ -237,6 +238,75 @@
   </si>
   <si>
     <t xml:space="preserve">east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Beast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed by name, so a reference to it carries a string.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">primary index, a string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">padding, so every table is one width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed by a number, so a reference to it carries an int.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">primary index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Howl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table BeastMove(key="BeastId,MoveId")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One row per pair; the key is both references taken together.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BeastId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Beast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a string-keyed target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoveId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">an int-keyed target</t>
   </si>
 </sst>
 </file>
@@ -765,4 +835,255 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:Q9"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" t="s">
+        <v>79</v>
+      </c>
+      <c r="N5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" t="s">
+        <v>93</v>
+      </c>
+      <c r="P5" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8" t="s">
+        <v>80</v>
+      </c>
+      <c r="P8" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="O9" t="s">
+        <v>82</v>
+      </c>
+      <c r="P9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test/fixtures/xlsx/composite-key/composite-key.xlsx
+++ b/test/fixtures/xlsx/composite-key/composite-key.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="109">
   <si>
     <t xml:space="preserve">:enum Slot</t>
   </si>
@@ -307,6 +307,42 @@
   </si>
   <si>
     <t xml:space="preserve">an int-keyed target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table BeastNote(key=BeastId)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed by a reference to a string-keyed table, named with `key=`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not the index, so `key=` has something to move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the index, and a reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grazes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table MoveNote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First column is the index and it is a reference to an int-keyed table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shoulder first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loud</t>
   </si>
 </sst>
 </file>
@@ -839,7 +875,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:Q9"/>
+  <dimension ref="B2:AC9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -861,6 +897,18 @@
       <c r="O2" t="s">
         <v>90</v>
       </c>
+      <c r="T2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
@@ -899,6 +947,30 @@
       <c r="Q3" t="s">
         <v>30</v>
       </c>
+      <c r="T3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
@@ -937,6 +1009,30 @@
       <c r="Q4" t="s">
         <v>24</v>
       </c>
+      <c r="T4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U4" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" t="s">
+        <v>92</v>
+      </c>
+      <c r="W4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
@@ -975,6 +1071,30 @@
       <c r="Q5" t="s">
         <v>31</v>
       </c>
+      <c r="T5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U5" t="s">
+        <v>100</v>
+      </c>
+      <c r="V5" t="s">
+        <v>101</v>
+      </c>
+      <c r="W5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
@@ -1013,6 +1133,30 @@
       <c r="Q6" t="s">
         <v>26</v>
       </c>
+      <c r="T6" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" t="s">
+        <v>26</v>
+      </c>
+      <c r="V6" t="s">
+        <v>26</v>
+      </c>
+      <c r="W6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
@@ -1042,6 +1186,24 @@
       <c r="Q7" t="s">
         <v>34</v>
       </c>
+      <c r="U7" t="s">
+        <v>10</v>
+      </c>
+      <c r="V7" t="s">
+        <v>80</v>
+      </c>
+      <c r="W7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
@@ -1070,6 +1232,24 @@
       </c>
       <c r="Q8" t="s">
         <v>36</v>
+      </c>
+      <c r="U8" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" t="s">
+        <v>82</v>
+      </c>
+      <c r="W8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
